--- a/content_forms/028_marketing_campaign_asset_upload_form--content_forms.xlsx
+++ b/content_forms/028_marketing_campaign_asset_upload_form--content_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'tag_1'}</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 1'}</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'tag_2'}</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 2'}</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'tag_3'}</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 3'}</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'tag_4'}</t>
+          <t>tag_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 4'}</t>
+          <t>Tag 4</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'tag_5'}</t>
+          <t>tag_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 5'}</t>
+          <t>Tag 5</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'tag_6'}</t>
+          <t>tag_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 6'}</t>
+          <t>Tag 6</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'tag_7'}</t>
+          <t>tag_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 7'}</t>
+          <t>Tag 7</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'tag_8'}</t>
+          <t>tag_8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 8'}</t>
+          <t>Tag 8</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'tag_9'}</t>
+          <t>tag_9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 9'}</t>
+          <t>Tag 9</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'tag_10'}</t>
+          <t>tag_10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 10'}</t>
+          <t>Tag 10</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'tag_11'}</t>
+          <t>tag_11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 11'}</t>
+          <t>Tag 11</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'tag_12'}</t>
+          <t>tag_12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 12'}</t>
+          <t>Tag 12</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'tag_13'}</t>
+          <t>tag_13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 13'}</t>
+          <t>Tag 13</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'tag_14'}</t>
+          <t>tag_14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 14'}</t>
+          <t>Tag 14</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'tag_15'}</t>
+          <t>tag_15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 15'}</t>
+          <t>Tag 15</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'tag_16'}</t>
+          <t>tag_16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 16'}</t>
+          <t>Tag 16</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'tag_17'}</t>
+          <t>tag_17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 17'}</t>
+          <t>Tag 17</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'tag_18'}</t>
+          <t>tag_18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 18'}</t>
+          <t>Tag 18</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'tag_19'}</t>
+          <t>tag_19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 19'}</t>
+          <t>Tag 19</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'tag_20'}</t>
+          <t>tag_20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 20'}</t>
+          <t>Tag 20</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'tag_21'}</t>
+          <t>tag_21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 21'}</t>
+          <t>Tag 21</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'tag_22'}</t>
+          <t>tag_22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 22'}</t>
+          <t>Tag 22</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'tag_23'}</t>
+          <t>tag_23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 23'}</t>
+          <t>Tag 23</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'tag_24'}</t>
+          <t>tag_24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 24'}</t>
+          <t>Tag 24</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'tag_25'}</t>
+          <t>tag_25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 25'}</t>
+          <t>Tag 25</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'tag_26'}</t>
+          <t>tag_26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 26'}</t>
+          <t>Tag 26</t>
         </is>
       </c>
     </row>
